--- a/data/trans_dic/P02E$otras-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P02E$otras-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros</t>
+          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 10,82</t>
+          <t>2,47; 11,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,48; 11,99</t>
+          <t>3,79; 12,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,72; 12,66</t>
+          <t>3,21; 12,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3,97; 10,5</t>
+          <t>4,16; 10,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,42; 8,13</t>
+          <t>3,48; 7,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,45; 12,28</t>
+          <t>4,19; 12,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,28; 9,32</t>
+          <t>4,34; 9,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,13; 8,23</t>
+          <t>4,09; 8,23</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,56; 10,72</t>
+          <t>4,81; 10,71</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,47; 8,36</t>
+          <t>3,49; 8,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,21; 6,55</t>
+          <t>3,11; 6,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,61; 6,37</t>
+          <t>2,68; 6,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,38; 8,44</t>
+          <t>4,19; 8,18</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,66; 6,55</t>
+          <t>3,67; 6,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,88; 11,47</t>
+          <t>7,04; 11,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,45; 7,57</t>
+          <t>4,38; 7,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,92; 6,1</t>
+          <t>3,84; 5,98</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,66; 8,54</t>
+          <t>5,53; 8,5</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,66; 26,32</t>
+          <t>12,86; 26,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,67; 10,64</t>
+          <t>2,75; 10,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,55; 12,55</t>
+          <t>3,55; 12,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,38; 9,38</t>
+          <t>2,31; 9,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,76; 10,43</t>
+          <t>3,71; 10,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,7; 18,22</t>
+          <t>8,41; 18,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,84; 15,3</t>
+          <t>8,04; 14,99</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,98; 9,05</t>
+          <t>3,82; 8,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,31; 14,21</t>
+          <t>7,48; 14,53</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,22; 10,39</t>
+          <t>6,35; 10,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,84; 6,82</t>
+          <t>3,85; 6,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,86; 7,18</t>
+          <t>3,72; 7,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,65; 7,68</t>
+          <t>4,85; 7,73</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,2; 6,66</t>
+          <t>4,17; 6,46</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,79; 11,37</t>
+          <t>7,75; 11,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,7; 8,26</t>
+          <t>5,69; 8,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,34; 6,18</t>
+          <t>4,41; 6,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,61; 9,13</t>
+          <t>6,58; 8,99</t>
         </is>
       </c>
     </row>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros</t>
+          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2612; 12257</t>
+          <t>2793; 13104</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6301; 21713</t>
+          <t>6869; 22472</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4740; 16151</t>
+          <t>4090; 16351</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10757; 28478</t>
+          <t>11278; 29033</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13295; 31570</t>
+          <t>13503; 31019</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8818; 24305</t>
+          <t>8292; 24008</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16440; 35818</t>
+          <t>16680; 36265</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>23518; 46875</t>
+          <t>23282; 46873</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14851; 34878</t>
+          <t>15666; 34855</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13421; 32330</t>
+          <t>13482; 32667</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20055; 40918</t>
+          <t>19452; 40659</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12553; 30605</t>
+          <t>12846; 30155</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24893; 47984</t>
+          <t>23803; 46498</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33147; 59297</t>
+          <t>33175; 58783</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>47971; 80023</t>
+          <t>49116; 77821</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>42543; 72264</t>
+          <t>41865; 69390</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>59986; 93299</t>
+          <t>58781; 91440</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>66618; 100528</t>
+          <t>65066; 100107</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15979; 33226</t>
+          <t>16237; 33927</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4730; 18831</t>
+          <t>4873; 18454</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5129; 18135</t>
+          <t>5127; 18354</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3964; 15598</t>
+          <t>3838; 15415</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8414; 23343</t>
+          <t>8314; 23968</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>18573; 38906</t>
+          <t>17967; 38437</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22945; 44758</t>
+          <t>23530; 43844</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15957; 36288</t>
+          <t>15320; 35332</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>26177; 50887</t>
+          <t>26794; 52037</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>38959; 65075</t>
+          <t>39746; 66857</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>37728; 67043</t>
+          <t>37831; 67543</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>29064; 54024</t>
+          <t>27997; 54221</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>46801; 77212</t>
+          <t>48783; 77764</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>63709; 100977</t>
+          <t>63294; 98066</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>86382; 126047</t>
+          <t>85956; 126572</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>93071; 134732</t>
+          <t>92870; 134030</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>108595; 154466</t>
+          <t>110305; 155878</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>122969; 169879</t>
+          <t>122457; 167309</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$otras-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P02E$otras-Estudios-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,47; 11,57</t>
+          <t>2,34; 10,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,79; 12,41</t>
+          <t>3,47; 12,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,21; 12,82</t>
+          <t>3,72; 12,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4,16; 10,71</t>
+          <t>4,35; 10,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,48; 7,99</t>
+          <t>3,37; 8,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,19; 12,13</t>
+          <t>4,12; 11,99</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,34; 9,43</t>
+          <t>4,33; 9,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,09; 8,23</t>
+          <t>4,16; 8,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>4,81; 10,71</t>
+          <t>4,66; 10,96</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,49; 8,45</t>
+          <t>3,44; 8,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,11; 6,51</t>
+          <t>3,26; 6,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,68; 6,28</t>
+          <t>2,68; 6,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,19; 8,18</t>
+          <t>4,33; 8,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,67; 6,5</t>
+          <t>3,54; 6,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,04; 11,16</t>
+          <t>6,86; 11,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,38; 7,27</t>
+          <t>4,48; 7,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,84; 5,98</t>
+          <t>3,88; 6,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,53; 8,5</t>
+          <t>5,66; 8,58</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>12,86; 26,88</t>
+          <t>13,02; 26,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,75; 10,42</t>
+          <t>2,74; 10,39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,55; 12,7</t>
+          <t>3,58; 12,65</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,31; 9,27</t>
+          <t>2,36; 9,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,71; 10,71</t>
+          <t>3,46; 10,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,41; 18,0</t>
+          <t>9,02; 18,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>8,04; 14,99</t>
+          <t>7,78; 15,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,82; 8,81</t>
+          <t>3,92; 8,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>7,48; 14,53</t>
+          <t>7,64; 14,35</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,35; 10,68</t>
+          <t>6,14; 10,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,85; 6,87</t>
+          <t>4,01; 6,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,72; 7,21</t>
+          <t>3,61; 6,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,85; 7,73</t>
+          <t>4,87; 7,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,17; 6,46</t>
+          <t>4,21; 6,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,75; 11,41</t>
+          <t>7,68; 11,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,69; 8,21</t>
+          <t>5,68; 8,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,41; 6,24</t>
+          <t>4,47; 6,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,58; 8,99</t>
+          <t>6,62; 9,06</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2793; 13104</t>
+          <t>2652; 11634</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6869; 22472</t>
+          <t>6278; 22657</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4090; 16351</t>
+          <t>4745; 16390</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11278; 29033</t>
+          <t>11785; 28729</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>13503; 31019</t>
+          <t>13101; 31262</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8292; 24008</t>
+          <t>8149; 23727</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16680; 36265</t>
+          <t>16627; 36968</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>23282; 46873</t>
+          <t>23702; 46241</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15666; 34855</t>
+          <t>15182; 35686</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>13482; 32667</t>
+          <t>13285; 32691</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>19452; 40659</t>
+          <t>20345; 40527</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12846; 30155</t>
+          <t>12858; 30187</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23803; 46498</t>
+          <t>24617; 47533</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>33175; 58783</t>
+          <t>32059; 59747</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49116; 77821</t>
+          <t>47813; 78847</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>41865; 69390</t>
+          <t>42792; 72101</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>58781; 91440</t>
+          <t>59429; 92226</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>65066; 100107</t>
+          <t>66660; 101057</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>16237; 33927</t>
+          <t>16432; 33779</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4873; 18454</t>
+          <t>4856; 18396</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5127; 18354</t>
+          <t>5179; 18284</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3838; 15415</t>
+          <t>3921; 15980</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8314; 23968</t>
+          <t>7750; 23946</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>17967; 38437</t>
+          <t>19255; 40166</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23530; 43844</t>
+          <t>22775; 44764</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>15320; 35332</t>
+          <t>15725; 34668</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>26794; 52037</t>
+          <t>27371; 51398</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39746; 66857</t>
+          <t>38436; 66471</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>37831; 67543</t>
+          <t>39467; 67508</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>27997; 54221</t>
+          <t>27138; 51420</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>48783; 77764</t>
+          <t>48958; 79429</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>63294; 98066</t>
+          <t>63874; 100401</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>85956; 126572</t>
+          <t>85168; 125318</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>92870; 134030</t>
+          <t>92771; 134876</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>110305; 155878</t>
+          <t>111724; 157161</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>122457; 167309</t>
+          <t>123156; 168541</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P02E$otras-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P02E$otras-Estudios-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros (tasa de respuesta: 96,71%)</t>
+          <t>Población con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1099,7 +1099,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros (tasa de respuesta: 96,71%)</t>
+          <t>Población con ayuda al cuidado por parte de, al menos, una persona externa que es familiar, amigo/a, vecino/a, u otros (tasa de respuesta: 96,71%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
